--- a/real-estate-data/Codebook_3_18.xlsx
+++ b/real-estate-data/Codebook_3_18.xlsx
@@ -727,7 +727,7 @@
   <cols>
     <col min="1" max="1" style="6" width="40.005" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="6" width="40.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="66.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="254.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="6" width="40.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
@@ -769,7 +769,7 @@
       </c>
       <c r="D3" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="32.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -781,7 +781,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="45.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="22.5" customFormat="1" s="1">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -795,7 +795,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="32.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25" customFormat="1" s="1">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -835,7 +835,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="256.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
